--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -40,9 +40,6 @@
     <t>&lt;name&gt;</t>
   </si>
   <si>
-    <t>Device Capacity</t>
-  </si>
-  <si>
     <t>Total Results in period</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
     <t>&lt;deviceCapacity&gt;</t>
   </si>
   <si>
-    <t>Utilization Rate</t>
-  </si>
-  <si>
     <t>&lt;utilizationRate&gt;</t>
   </si>
   <si>
@@ -62,6 +56,12 @@
   </si>
   <si>
     <t>Device Utilization per Day, number of tests</t>
+  </si>
+  <si>
+    <t>Daily Device Capacity</t>
+  </si>
+  <si>
+    <t>Utilization Rate (excluding weekends)</t>
   </si>
 </sst>
 </file>
@@ -616,13 +616,13 @@
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
     <col min="2" max="2" width="12.796875" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.69921875" customWidth="1"/>
+    <col min="4" max="4" width="21.3984375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -653,13 +653,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -667,13 +667,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -688,15 +688,14 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="12.796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.296875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -724,13 +723,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -738,13 +737,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-2\api\templates\device_utilization_per_day\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\device_utilization_per_day\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>Utilization Rate (excluding weekends)</t>
+  </si>
+  <si>
+    <t>&lt;StatesLabel&gt;: &lt;States&gt;</t>
+  </si>
+  <si>
+    <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
   </si>
 </sst>
 </file>
@@ -632,12 +638,12 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">

--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -126,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -149,6 +149,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -195,7 +224,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -208,6 +237,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -617,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.796875" customWidth="1"/>
@@ -653,36 +691,51 @@
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="B6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -12,15 +12,14 @@
     <workbookView xWindow="35568" yWindow="1332" windowWidth="22992" windowHeight="16080" tabRatio="815"/>
   </bookViews>
   <sheets>
-    <sheet name="Utilization Raw Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Utilization Percentage" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913" fullPrecision="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>&lt;Table&gt;</t>
   </si>
@@ -28,15 +27,9 @@
     <t>Dates: &lt;Dates&gt;</t>
   </si>
   <si>
-    <t>States: &lt;States&gt;</t>
-  </si>
-  <si>
     <t>Device</t>
   </si>
   <si>
-    <t>LGA: &lt;Lgas&gt;</t>
-  </si>
-  <si>
     <t>&lt;name&gt;</t>
   </si>
   <si>
@@ -52,12 +45,6 @@
     <t>&lt;utilizationRate&gt;</t>
   </si>
   <si>
-    <t>Device Utilization per Day, percentage</t>
-  </si>
-  <si>
-    <t>Device Utilization per Day, number of tests</t>
-  </si>
-  <si>
     <t>Daily Device Capacity</t>
   </si>
   <si>
@@ -68,6 +55,9 @@
   </si>
   <si>
     <t>&lt;LgasLabel&gt;: &lt;Lgas&gt;</t>
+  </si>
+  <si>
+    <t>Device Utilization per Day, number of tests and percentage</t>
   </si>
 </sst>
 </file>
@@ -126,27 +116,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -224,28 +199,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -666,7 +634,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -676,12 +644,12 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -696,37 +664,37 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -739,74 +707,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="31.796875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="12.796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.296875" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="11" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -1,15 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91629D92-EBED-5447-91CA-B10FA639BA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -67,36 +69,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <family val="2"/>
-      <sz val="16"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <charset val="1"/>
-      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -113,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -122,16 +124,43 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium"/>
-      <bottom/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin"/>
-      <top style="medium"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -139,25 +168,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1" shrinkToFit="1"/>
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -176,47 +211,362 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.015625" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.8" customWidth="1"/>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12.8" customWidth="1"/>
-    <col min="4" max="4" width="12.7" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.4" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="15.6" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" ht="16.2" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -224,51 +574,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="19.8" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:5" ht="19.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="15.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" ht="15.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="9" spans="1:5" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="E12" s="1"/>
     </row>
   </sheetData>
@@ -280,6 +630,6 @@
     <mergeCell ref="E8:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91629D92-EBED-5447-91CA-B10FA639BA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Device Utilization per Day, number of tests and percentage</t>
   </si>
@@ -33,15 +31,18 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
+    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+  </si>
+  <si>
     <t>&lt;Table&gt;</t>
   </si>
   <si>
+    <t>Site</t>
+  </si>
+  <si>
     <t>Device</t>
   </si>
   <si>
-    <t>Site</t>
-  </si>
-  <si>
     <t>Total Results in period</t>
   </si>
   <si>
@@ -51,10 +52,10 @@
     <t>Utilization Rate (excluding weekends)</t>
   </si>
   <si>
+    <t>&lt;siteName&gt;</t>
+  </si>
+  <si>
     <t>&lt;name&gt;</t>
-  </si>
-  <si>
-    <t>&lt;siteName&gt;</t>
   </si>
   <si>
     <t>&lt;totalResults&gt;</t>
@@ -69,36 +70,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -124,44 +125,24 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -176,23 +157,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,9 +508,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="11" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.83203125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -538,87 +519,89 @@
     <col min="5" max="5" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="16.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" ht="19.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" ht="15.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="15.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="E10" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" ht="16" customHeight="1" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E12" s="1"/>
     </row>
   </sheetData>
@@ -630,6 +613,6 @@
     <mergeCell ref="E8:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -151,9 +151,7 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>

--- a/api/templates/device_utilization_per_day/en.xlsx
+++ b/api/templates/device_utilization_per_day/en.xlsx
@@ -31,7 +31,7 @@
     <t>&lt;SitesLabel&gt;: &lt;Sites&gt;</t>
   </si>
   <si>
-    <t>&lt;DecommissionedDevicesLabel&gt;: &lt;DecommissionedDevices&gt;</t>
+    <t>Decommissioned Devices: &lt;DecommissionedDevices&gt;</t>
   </si>
   <si>
     <t>&lt;Table&gt;</t>
@@ -151,7 +151,7 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" shrinkToFit="1"/>
     </xf>
